--- a/Outputs/Scenarios/PtX_demand_DK_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DK_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004952914075622283</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00519560489102166</v>
+        <v>0.002877396064777138</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00173186829700722</v>
+        <v>0.004047361794181274</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>7.136310795228682e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00173186829700722</v>
+        <v>0.001734583626077689</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0007332186289504282</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02800134467229686</v>
+        <v>0.01550752234985518</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.009333781557432289</v>
+        <v>0.02181296980611438</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>3.85904541552857e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.009333781557432289</v>
+        <v>0.009348415631191879</v>
       </c>
     </row>
     <row r="43">
